--- a/product_surveys/019_wheel_survey_form--product_surveys.xlsx
+++ b/product_surveys/019_wheel_survey_form--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wheel Survey Form</t>
+          <t>Overall Impression</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,20 +548,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Product Quality</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Satisfaction</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Helpful Features</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Additional</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Unhelpful Features</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Suggestions</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Satisfaction</t>
+          <t>Repurchase</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,57 +732,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Additional Feedback</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>page_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>page_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -799,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'product_1'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Product 1'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -849,29 +803,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'product_2'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Product 2'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'product_3'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Product 3'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -883,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -900,301 +854,131 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Neutral'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'bad'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Bad'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_7_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page_7_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>page_7_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'neutral'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Neutral'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>page_8_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>page_8_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'good'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>page_8_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'neutral'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Neutral'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>page_11_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'product_1'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Product 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>page_11_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'product_2'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Product 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>page_11_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'product_3'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Product 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>page_12_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>page_12_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'good'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>page_12_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'neutral'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Neutral'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
